--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220681</v>
+        <v>113220762</v>
       </c>
       <c r="B3" t="n">
-        <v>56891</v>
+        <v>57522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,57 +830,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103035</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317899</v>
+        <v>318035</v>
       </c>
       <c r="R3" t="n">
-        <v>6444721</v>
+        <v>6444918</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -909,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -919,7 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +934,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -946,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220762</v>
+        <v>113220619</v>
       </c>
       <c r="B4" t="n">
-        <v>57522</v>
+        <v>56908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,20 +965,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208260</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -981,35 +988,34 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318035</v>
+        <v>317897</v>
       </c>
       <c r="R4" t="n">
-        <v>6444918</v>
+        <v>6444648</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1048,12 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1063,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220619</v>
+        <v>113220681</v>
       </c>
       <c r="B6" t="n">
-        <v>56908</v>
+        <v>56891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103035</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317897</v>
+        <v>317899</v>
       </c>
       <c r="R6" t="n">
-        <v>6444648</v>
+        <v>6444721</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113325868</v>
+        <v>113325872</v>
       </c>
       <c r="B7" t="n">
-        <v>55976</v>
+        <v>55826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,12 +1373,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325872</v>
+        <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55826</v>
+        <v>55976</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,20 +1469,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1488,16 +1492,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399389</v>
+        <v>113399377</v>
       </c>
       <c r="B9" t="n">
-        <v>56781</v>
+        <v>93755</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317917</v>
+        <v>318044</v>
       </c>
       <c r="R9" t="n">
-        <v>6444177</v>
+        <v>6444894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,11 +1648,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B10" t="n">
         <v>56781</v>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1786,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399375</v>
+        <v>113399389</v>
       </c>
       <c r="B11" t="n">
-        <v>93739</v>
+        <v>56781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,25 +1793,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>318044</v>
+        <v>317917</v>
       </c>
       <c r="R11" t="n">
-        <v>6444894</v>
+        <v>6444177</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399392</v>
+        <v>113399388</v>
       </c>
       <c r="B12" t="n">
         <v>56781</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317703</v>
+        <v>317879</v>
       </c>
       <c r="R12" t="n">
-        <v>6444361</v>
+        <v>6444178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -953,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220619</v>
+        <v>113220681</v>
       </c>
       <c r="B4" t="n">
-        <v>56908</v>
+        <v>56891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,33 +969,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317897</v>
+        <v>317899</v>
       </c>
       <c r="R4" t="n">
-        <v>6444648</v>
+        <v>6444721</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220681</v>
+        <v>113220619</v>
       </c>
       <c r="B6" t="n">
-        <v>56891</v>
+        <v>56908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103035</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317899</v>
+        <v>317897</v>
       </c>
       <c r="R6" t="n">
-        <v>6444721</v>
+        <v>6444648</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1572,7 +1572,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399377</v>
+        <v>113399374</v>
       </c>
       <c r="B9" t="n">
         <v>93755</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399392</v>
+        <v>113399389</v>
       </c>
       <c r="B10" t="n">
         <v>56781</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317703</v>
+        <v>317917</v>
       </c>
       <c r="R10" t="n">
-        <v>6444361</v>
+        <v>6444177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399389</v>
+        <v>113399388</v>
       </c>
       <c r="B11" t="n">
         <v>56781</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317917</v>
+        <v>317879</v>
       </c>
       <c r="R11" t="n">
-        <v>6444177</v>
+        <v>6444178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B12" t="n">
         <v>56781</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R12" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113217885</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>113220762</v>
       </c>
       <c r="B3" t="n">
-        <v>57522</v>
+        <v>57523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>113220681</v>
       </c>
       <c r="B4" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113221183</v>
+        <v>113220619</v>
       </c>
       <c r="B5" t="n">
-        <v>56656</v>
+        <v>56909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1116,27 +1116,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317957</v>
+        <v>317897</v>
       </c>
       <c r="R5" t="n">
-        <v>6444661</v>
+        <v>6444648</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1168,7 +1172,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1178,12 +1182,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220619</v>
+        <v>113221183</v>
       </c>
       <c r="B6" t="n">
-        <v>56908</v>
+        <v>56657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,16 +1225,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1245,31 +1244,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317897</v>
+        <v>317957</v>
       </c>
       <c r="R6" t="n">
-        <v>6444648</v>
+        <v>6444661</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1301,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1311,7 +1306,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1460,7 +1460,7 @@
         <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55976</v>
+        <v>55977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399374</v>
+        <v>113399372</v>
       </c>
       <c r="B9" t="n">
-        <v>93755</v>
+        <v>93767</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399389</v>
+        <v>113399392</v>
       </c>
       <c r="B10" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317917</v>
+        <v>317703</v>
       </c>
       <c r="R10" t="n">
-        <v>6444177</v>
+        <v>6444361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
         <v>113399388</v>
       </c>
       <c r="B11" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399392</v>
+        <v>113399389</v>
       </c>
       <c r="B12" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317703</v>
+        <v>317917</v>
       </c>
       <c r="R12" t="n">
-        <v>6444361</v>
+        <v>6444177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220762</v>
+        <v>113221183</v>
       </c>
       <c r="B3" t="n">
-        <v>57523</v>
+        <v>56657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,19 +853,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -875,13 +870,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318035</v>
+        <v>317957</v>
       </c>
       <c r="R3" t="n">
-        <v>6444918</v>
+        <v>6444661</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,7 +905,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,12 +915,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -953,10 +947,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220681</v>
+        <v>113220619</v>
       </c>
       <c r="B4" t="n">
-        <v>56892</v>
+        <v>56909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,33 +963,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,10 +1003,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317899</v>
+        <v>317897</v>
       </c>
       <c r="R4" t="n">
-        <v>6444721</v>
+        <v>6444648</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,7 +1038,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,7 +1048,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1081,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113220619</v>
+        <v>113220681</v>
       </c>
       <c r="B5" t="n">
-        <v>56909</v>
+        <v>56892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1097,33 +1091,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103035</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1137,10 +1131,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317897</v>
+        <v>317899</v>
       </c>
       <c r="R5" t="n">
-        <v>6444648</v>
+        <v>6444721</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1172,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1182,7 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113221183</v>
+        <v>113220762</v>
       </c>
       <c r="B6" t="n">
-        <v>56657</v>
+        <v>57523</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,20 +1215,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>208260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1244,14 +1238,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1261,13 +1260,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317957</v>
+        <v>318035</v>
       </c>
       <c r="R6" t="n">
-        <v>6444661</v>
+        <v>6444918</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1296,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1306,12 +1305,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,6 +1319,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113325872</v>
+        <v>113325868</v>
       </c>
       <c r="B7" t="n">
-        <v>55826</v>
+        <v>55977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,16 +1373,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1457,10 +1453,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325868</v>
+        <v>113325872</v>
       </c>
       <c r="B8" t="n">
-        <v>55977</v>
+        <v>55826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,20 +1465,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1492,12 +1488,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399392</v>
+        <v>113399389</v>
       </c>
       <c r="B10" t="n">
         <v>56782</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317703</v>
+        <v>317917</v>
       </c>
       <c r="R10" t="n">
-        <v>6444361</v>
+        <v>6444177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399389</v>
+        <v>113399392</v>
       </c>
       <c r="B12" t="n">
         <v>56782</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317917</v>
+        <v>317703</v>
       </c>
       <c r="R12" t="n">
-        <v>6444177</v>
+        <v>6444361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113221183</v>
+        <v>113220762</v>
       </c>
       <c r="B3" t="n">
-        <v>56657</v>
+        <v>57523</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,14 +853,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -870,13 +875,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317957</v>
+        <v>318035</v>
       </c>
       <c r="R3" t="n">
-        <v>6444661</v>
+        <v>6444918</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,12 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,6 +934,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -947,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220619</v>
+        <v>113221183</v>
       </c>
       <c r="B4" t="n">
-        <v>56909</v>
+        <v>56657</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -963,16 +969,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -982,31 +988,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317897</v>
+        <v>317957</v>
       </c>
       <c r="R4" t="n">
-        <v>6444648</v>
+        <v>6444661</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1038,7 +1040,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1048,7 +1050,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1203,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220762</v>
+        <v>113220619</v>
       </c>
       <c r="B6" t="n">
-        <v>57523</v>
+        <v>56909</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,20 +1222,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208260</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1238,35 +1245,34 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318035</v>
+        <v>317897</v>
       </c>
       <c r="R6" t="n">
-        <v>6444918</v>
+        <v>6444648</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1295,7 +1301,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1305,12 +1311,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1320,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113325868</v>
+        <v>113325872</v>
       </c>
       <c r="B7" t="n">
-        <v>55977</v>
+        <v>55826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,12 +1373,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325872</v>
+        <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55826</v>
+        <v>55977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,20 +1469,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1488,16 +1492,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399372</v>
+        <v>113399378</v>
       </c>
       <c r="B9" t="n">
-        <v>93767</v>
+        <v>93789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399389</v>
+        <v>113399392</v>
       </c>
       <c r="B10" t="n">
         <v>56782</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317917</v>
+        <v>317703</v>
       </c>
       <c r="R10" t="n">
-        <v>6444177</v>
+        <v>6444361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399392</v>
+        <v>113399389</v>
       </c>
       <c r="B12" t="n">
         <v>56782</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317703</v>
+        <v>317917</v>
       </c>
       <c r="R12" t="n">
-        <v>6444361</v>
+        <v>6444177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113217885</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220762</v>
+        <v>113220619</v>
       </c>
       <c r="B3" t="n">
-        <v>57523</v>
+        <v>56912</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,35 +853,34 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318035</v>
+        <v>317897</v>
       </c>
       <c r="R3" t="n">
-        <v>6444918</v>
+        <v>6444648</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,7 +909,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,12 +919,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +928,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -953,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113221183</v>
+        <v>113220762</v>
       </c>
       <c r="B4" t="n">
-        <v>56657</v>
+        <v>57526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,20 +958,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>208260</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -988,14 +981,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>fragment</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1005,13 +1003,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317957</v>
+        <v>318035</v>
       </c>
       <c r="R4" t="n">
-        <v>6444661</v>
+        <v>6444918</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1040,7 +1038,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1050,12 +1048,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,6 +1062,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1082,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113220681</v>
+        <v>113221183</v>
       </c>
       <c r="B5" t="n">
-        <v>56892</v>
+        <v>56660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,21 +1097,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103035</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1127,21 +1126,17 @@
           <t>stationär</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317899</v>
+        <v>317957</v>
       </c>
       <c r="R5" t="n">
-        <v>6444721</v>
+        <v>6444661</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1173,7 +1168,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1183,7 +1178,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220619</v>
+        <v>113220681</v>
       </c>
       <c r="B6" t="n">
-        <v>56909</v>
+        <v>56895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103035</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317897</v>
+        <v>317899</v>
       </c>
       <c r="R6" t="n">
-        <v>6444648</v>
+        <v>6444721</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113325872</v>
+        <v>113325868</v>
       </c>
       <c r="B7" t="n">
-        <v>55826</v>
+        <v>55980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,16 +1373,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1430,7 +1426,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1457,10 +1453,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325868</v>
+        <v>113325872</v>
       </c>
       <c r="B8" t="n">
-        <v>55977</v>
+        <v>55829</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1469,20 +1465,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1492,12 +1488,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399378</v>
+        <v>113399377</v>
       </c>
       <c r="B9" t="n">
-        <v>93789</v>
+        <v>93793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399392</v>
+        <v>113399388</v>
       </c>
       <c r="B10" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317703</v>
+        <v>317879</v>
       </c>
       <c r="R10" t="n">
-        <v>6444361</v>
+        <v>6444178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B11" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R11" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1891,7 +1891,7 @@
         <v>113399389</v>
       </c>
       <c r="B12" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113217885</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220619</v>
+        <v>113220762</v>
       </c>
       <c r="B3" t="n">
-        <v>56912</v>
+        <v>57530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,34 +853,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317897</v>
+        <v>318035</v>
       </c>
       <c r="R3" t="n">
-        <v>6444648</v>
+        <v>6444918</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -909,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -919,7 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +934,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -946,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220762</v>
+        <v>113220619</v>
       </c>
       <c r="B4" t="n">
-        <v>57526</v>
+        <v>56916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,20 +965,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208260</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -981,35 +988,34 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>318035</v>
+        <v>317897</v>
       </c>
       <c r="R4" t="n">
-        <v>6444918</v>
+        <v>6444648</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1048,12 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,7 +1063,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>113221183</v>
       </c>
       <c r="B5" t="n">
-        <v>56660</v>
+        <v>56664</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>113220681</v>
       </c>
       <c r="B6" t="n">
-        <v>56895</v>
+        <v>56899</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B10" t="n">
         <v>56785</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399392</v>
+        <v>113399389</v>
       </c>
       <c r="B11" t="n">
         <v>56785</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317703</v>
+        <v>317917</v>
       </c>
       <c r="R11" t="n">
-        <v>6444361</v>
+        <v>6444177</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399389</v>
+        <v>113399388</v>
       </c>
       <c r="B12" t="n">
         <v>56785</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317917</v>
+        <v>317879</v>
       </c>
       <c r="R12" t="n">
-        <v>6444177</v>
+        <v>6444178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>113325868</v>
       </c>
       <c r="B7" t="n">
-        <v>55980</v>
+        <v>55984</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>113325872</v>
       </c>
       <c r="B8" t="n">
-        <v>55829</v>
+        <v>55833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399377</v>
+        <v>113399392</v>
       </c>
       <c r="B9" t="n">
-        <v>93793</v>
+        <v>56789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318044</v>
+        <v>317703</v>
       </c>
       <c r="R9" t="n">
-        <v>6444894</v>
+        <v>6444361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,6 +1648,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,10 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399392</v>
+        <v>113399372</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>93799</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,25 +1691,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317703</v>
+        <v>318044</v>
       </c>
       <c r="R10" t="n">
-        <v>6444361</v>
+        <v>6444894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,11 +1755,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399389</v>
+        <v>113399388</v>
       </c>
       <c r="B11" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317917</v>
+        <v>317879</v>
       </c>
       <c r="R11" t="n">
-        <v>6444177</v>
+        <v>6444178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399388</v>
+        <v>113399389</v>
       </c>
       <c r="B12" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317879</v>
+        <v>317917</v>
       </c>
       <c r="R12" t="n">
-        <v>6444178</v>
+        <v>6444177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220762</v>
+        <v>113220619</v>
       </c>
       <c r="B3" t="n">
-        <v>57530</v>
+        <v>56916</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,35 +853,34 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318035</v>
+        <v>317897</v>
       </c>
       <c r="R3" t="n">
-        <v>6444918</v>
+        <v>6444648</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -910,7 +909,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -920,12 +919,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +928,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -953,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220619</v>
+        <v>113220681</v>
       </c>
       <c r="B4" t="n">
-        <v>56916</v>
+        <v>56899</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,33 +962,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103035</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1009,10 +1002,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317897</v>
+        <v>317899</v>
       </c>
       <c r="R4" t="n">
-        <v>6444648</v>
+        <v>6444721</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,7 +1037,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,7 +1047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1210,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220681</v>
+        <v>113220762</v>
       </c>
       <c r="B6" t="n">
-        <v>56899</v>
+        <v>57530</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,57 +1215,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103035</v>
+        <v>208260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317899</v>
+        <v>318035</v>
       </c>
       <c r="R6" t="n">
-        <v>6444721</v>
+        <v>6444918</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1301,7 +1295,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1311,7 +1305,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,6 +1319,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113325868</v>
+        <v>113325872</v>
       </c>
       <c r="B7" t="n">
-        <v>55984</v>
+        <v>55833</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,20 +1350,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100045</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1373,12 +1373,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1426,7 +1430,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1453,10 +1457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325872</v>
+        <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55833</v>
+        <v>55984</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1465,20 +1469,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100045</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1488,16 +1492,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399392</v>
+        <v>113399378</v>
       </c>
       <c r="B9" t="n">
-        <v>56789</v>
+        <v>93799</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317703</v>
+        <v>318044</v>
       </c>
       <c r="R9" t="n">
-        <v>6444361</v>
+        <v>6444894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,11 +1648,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399372</v>
+        <v>113399388</v>
       </c>
       <c r="B10" t="n">
-        <v>93799</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,25 +1686,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318044</v>
+        <v>317879</v>
       </c>
       <c r="R10" t="n">
-        <v>6444894</v>
+        <v>6444178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1755,6 +1750,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B11" t="n">
         <v>56789</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R11" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220681</v>
+        <v>113221183</v>
       </c>
       <c r="B4" t="n">
-        <v>56899</v>
+        <v>56664</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,21 +962,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103035</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -991,21 +991,17 @@
           <t>stationär</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317899</v>
+        <v>317957</v>
       </c>
       <c r="R4" t="n">
-        <v>6444721</v>
+        <v>6444661</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1037,7 +1033,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,7 +1043,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,10 +1075,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113221183</v>
+        <v>113220681</v>
       </c>
       <c r="B5" t="n">
-        <v>56664</v>
+        <v>56899</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1090,21 +1091,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100001</v>
+        <v>103035</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1119,17 +1120,21 @@
           <t>stationär</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317957</v>
+        <v>317899</v>
       </c>
       <c r="R5" t="n">
-        <v>6444661</v>
+        <v>6444721</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1161,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1171,12 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1993,6 +1993,139 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113610161</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56001</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Ödsmål, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>317981</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6444841</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Möjligen tjäderhöna, uppflog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Arell</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Arell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -818,10 +818,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220619</v>
+        <v>113220762</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,20 +830,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -853,34 +853,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317897</v>
+        <v>318035</v>
       </c>
       <c r="R3" t="n">
-        <v>6444648</v>
+        <v>6444918</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -909,7 +910,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -919,7 +920,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +934,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -946,10 +953,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113221183</v>
+        <v>113220619</v>
       </c>
       <c r="B4" t="n">
-        <v>56664</v>
+        <v>56923</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,16 +969,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -981,27 +988,31 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317957</v>
+        <v>317897</v>
       </c>
       <c r="R4" t="n">
-        <v>6444661</v>
+        <v>6444648</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1033,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1043,12 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1084,7 @@
         <v>113220681</v>
       </c>
       <c r="B5" t="n">
-        <v>56899</v>
+        <v>56906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1203,10 +1209,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113220762</v>
+        <v>113221183</v>
       </c>
       <c r="B6" t="n">
-        <v>57530</v>
+        <v>56671</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,20 +1221,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208260</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1238,19 +1244,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>fragment</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1260,13 +1261,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>318035</v>
+        <v>317957</v>
       </c>
       <c r="R6" t="n">
-        <v>6444918</v>
+        <v>6444661</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1295,7 +1296,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1305,12 +1306,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1320,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>113325872</v>
       </c>
       <c r="B7" t="n">
-        <v>55833</v>
+        <v>55840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55984</v>
+        <v>55991</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399378</v>
+        <v>113399389</v>
       </c>
       <c r="B9" t="n">
-        <v>93799</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318044</v>
+        <v>317917</v>
       </c>
       <c r="R9" t="n">
-        <v>6444894</v>
+        <v>6444177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,6 +1648,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,10 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B10" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1781,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399392</v>
+        <v>113399375</v>
       </c>
       <c r="B11" t="n">
-        <v>56789</v>
+        <v>93806</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,25 +1798,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1821,10 +1826,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317703</v>
+        <v>318044</v>
       </c>
       <c r="R11" t="n">
-        <v>6444361</v>
+        <v>6444894</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,11 +1862,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399389</v>
+        <v>113399388</v>
       </c>
       <c r="B12" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317917</v>
+        <v>317879</v>
       </c>
       <c r="R12" t="n">
-        <v>6444177</v>
+        <v>6444178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>113610161</v>
       </c>
       <c r="B13" t="n">
-        <v>56001</v>
+        <v>56002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>113325872</v>
       </c>
       <c r="B7" t="n">
-        <v>55840</v>
+        <v>55842</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>113325868</v>
       </c>
       <c r="B8" t="n">
-        <v>55991</v>
+        <v>55993</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399389</v>
+        <v>113399373</v>
       </c>
       <c r="B9" t="n">
-        <v>56796</v>
+        <v>93811</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317917</v>
+        <v>318044</v>
       </c>
       <c r="R9" t="n">
-        <v>6444177</v>
+        <v>6444894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,11 +1648,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399392</v>
+        <v>113399388</v>
       </c>
       <c r="B10" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317703</v>
+        <v>317879</v>
       </c>
       <c r="R10" t="n">
-        <v>6444361</v>
+        <v>6444178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1786,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399375</v>
+        <v>113399389</v>
       </c>
       <c r="B11" t="n">
-        <v>93806</v>
+        <v>56798</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,25 +1793,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>318044</v>
+        <v>317917</v>
       </c>
       <c r="R11" t="n">
-        <v>6444894</v>
+        <v>6444177</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,6 +1857,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,10 +1888,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399388</v>
+        <v>113399392</v>
       </c>
       <c r="B12" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317879</v>
+        <v>317703</v>
       </c>
       <c r="R12" t="n">
-        <v>6444178</v>
+        <v>6444361</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
         <v>113610161</v>
       </c>
       <c r="B13" t="n">
-        <v>56002</v>
+        <v>56004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399373</v>
+        <v>113399388</v>
       </c>
       <c r="B9" t="n">
-        <v>93811</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318044</v>
+        <v>317879</v>
       </c>
       <c r="R9" t="n">
-        <v>6444894</v>
+        <v>6444178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,6 +1648,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,10 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113399373</v>
       </c>
       <c r="B10" t="n">
-        <v>56798</v>
+        <v>93811</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,25 +1691,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>318044</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,11 +1755,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399388</v>
+        <v>113399373</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>93839</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317879</v>
+        <v>318044</v>
       </c>
       <c r="R9" t="n">
-        <v>6444178</v>
+        <v>6444894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,11 +1648,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1679,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399373</v>
+        <v>113399388</v>
       </c>
       <c r="B10" t="n">
-        <v>93811</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1691,25 +1686,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1719,10 +1714,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>318044</v>
+        <v>317879</v>
       </c>
       <c r="R10" t="n">
-        <v>6444894</v>
+        <v>6444178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1755,6 +1750,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,7 +1784,7 @@
         <v>113399389</v>
       </c>
       <c r="B11" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>113399392</v>
       </c>
       <c r="B12" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>113610161</v>
       </c>
       <c r="B13" t="n">
-        <v>56004</v>
+        <v>56032</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -1572,10 +1572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113399373</v>
+        <v>113399389</v>
       </c>
       <c r="B9" t="n">
-        <v>93839</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>318044</v>
+        <v>317917</v>
       </c>
       <c r="R9" t="n">
-        <v>6444894</v>
+        <v>6444177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1648,6 +1648,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,10 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113399376</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>93839</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,25 +1691,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1714,10 +1719,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>318044</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,11 +1755,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-11-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399389</v>
+        <v>113399388</v>
       </c>
       <c r="B11" t="n">
         <v>56826</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317917</v>
+        <v>317879</v>
       </c>
       <c r="R11" t="n">
-        <v>6444177</v>
+        <v>6444178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113217885</v>
+        <v>113258470</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317950</v>
+        <v>318022</v>
       </c>
       <c r="R2" t="n">
-        <v>6444792</v>
+        <v>6444680</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med karakteristiskt rop</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,18 +776,9 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsområde med flera äldre granar och tallar med inslag av ek och div andra lövträd. Finns sumpskogskaraktärer och e del död ved.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -818,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113220762</v>
+        <v>113399385</v>
       </c>
       <c r="B3" t="n">
-        <v>56252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,54 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>fragment</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>318035</v>
+        <v>318027</v>
       </c>
       <c r="R3" t="n">
-        <v>6444918</v>
+        <v>6444643</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,63 +860,42 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113220494</v>
+        <v>113399386</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,53 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317918</v>
+        <v>318032</v>
       </c>
       <c r="R4" t="n">
-        <v>6444656</v>
+        <v>6444666</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,27 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Räknade upp till 7 individer som födosökte på granarna.</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,27 +977,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113221041</v>
+        <v>113399387</v>
       </c>
       <c r="B5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,45 +1000,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>317988</v>
+        <v>318021</v>
       </c>
       <c r="R5" t="n">
-        <v>6444673</v>
+        <v>6444698</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1164,22 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,77 +1074,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113221183</v>
+        <v>113399372</v>
       </c>
       <c r="B6" t="n">
-        <v>57156</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317957</v>
+        <v>318044</v>
       </c>
       <c r="R6" t="n">
-        <v>6444661</v>
+        <v>6444894</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1288,27 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1323,27 +1171,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emily Macgregor</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113220619</v>
+        <v>119937591</v>
       </c>
       <c r="B7" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,53 +1194,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smällen, Boh</t>
+          <t>Smällen, Smällen, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317897</v>
+        <v>318054</v>
       </c>
       <c r="R7" t="n">
-        <v>6444647</v>
+        <v>6444796</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1421,22 +1257,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1463,37 +1299,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113325868</v>
+        <v>113325904</v>
       </c>
       <c r="B8" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1501,9 +1332,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1511,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317967</v>
+        <v>318016</v>
       </c>
       <c r="R8" t="n">
-        <v>6444846</v>
+        <v>6444685</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1549,17 +1383,13 @@
           <t>2023-11-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1578,32 +1408,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113325872</v>
+        <v>113221183</v>
       </c>
       <c r="B9" t="n">
-        <v>56323</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100045</v>
+        <v>100001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1613,14 +1438,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1630,13 +1455,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317967</v>
+        <v>317957</v>
       </c>
       <c r="R9" t="n">
-        <v>6444846</v>
+        <v>6444661</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1660,17 +1485,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Förbiflygande grupp sångsvanar</t>
+          <t>Sittande duvhök i barrträd. Relativt stor! Grå/vit. Flög sedan iväg öster ut när jag gick förbi.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,32 +1532,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113399388</v>
+        <v>113325872</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1730,20 +1560,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317879</v>
+        <v>317967</v>
       </c>
       <c r="R10" t="n">
-        <v>6444178</v>
+        <v>6444846</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,17 +1609,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Förbiflygande grupp sångsvanar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,27 +1634,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113399378</v>
+        <v>113217885</v>
       </c>
       <c r="B11" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,34 +1657,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>318044</v>
+        <v>317950</v>
       </c>
       <c r="R11" t="n">
-        <v>6444894</v>
+        <v>6444792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,12 +1727,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med karakteristiskt rop</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,35 +1758,40 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsområde med flera äldre granar och tallar med inslag av ek och div andra lövträd. Finns sumpskogskaraktärer och e del död ved.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Emily Macgregor</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113399392</v>
+        <v>113399388</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1946,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317702</v>
+        <v>317879</v>
       </c>
       <c r="R12" t="n">
-        <v>6444362</v>
+        <v>6444178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2016,16 +1889,11 @@
         <v>113399389</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2120,15 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113610161</v>
+        <v>113399392</v>
       </c>
       <c r="B14" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,16 +1999,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2153,36 +2016,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bräcke skog, Ödsmål, Stenungsund, Boh</t>
+          <t>Smällen, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>317980</v>
+        <v>317702</v>
       </c>
       <c r="R14" t="n">
-        <v>6444841</v>
+        <v>6444362</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2206,34 +2053,24 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Möjligen tjäderhöna, uppflog</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2241,12 +2078,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Arell</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Arell</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2256,16 +2093,11 @@
         <v>115283409</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2361,6 +2193,1420 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126130801</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bräcke Skog 402, 444 95 Ödsmål, Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>317707</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6444220</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Christian Freij</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Christian Freij</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113325868</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>317967</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6444846</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppflyg av hönsfågel, hona. Osäkerhet kring artbestämning om det kan var orre eller järpe</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113610161</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bräcke skog, Ödsmål, Stenungsund, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>317980</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6444841</v>
+      </c>
+      <c r="S18" t="n">
+        <v>100</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-11-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Möjligen tjäderhöna, uppflog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Arell</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Arell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113220494</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>317918</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6444656</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Räknade upp till 7 individer som födosökte på granarna.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113399397</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>318035</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6444683</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113220619</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>317897</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6444647</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113220964</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>318044</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6444797</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113221034</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>318044</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6444797</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113221041</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>317988</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6444673</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113220681</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>317899</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6444720</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113220716</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>318018</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6444900</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113220762</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>fragment</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Smällen, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>318035</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6444918</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Stenungsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ödsmål</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hittade två skelett från orm, troligen huggorm pga storleken. Men jag är osäker. Snok finns i området med sedan tidigare vet jag. Så det kan finnas en chans för andra ormarter också. Gissar att de blivit dödade av häckande ormvråkspar precis i närheten.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46483-2023 artfynd.xlsx
+++ b/artfynd/A 46483-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113258470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399385</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399387</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119937591</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113325904</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113221183</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113325872</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113217885</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399388</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1985,6 +2045,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399389</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115283409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2300,6 +2375,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126130801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,6 +2490,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113325868</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2538,6 +2623,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113610161</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2666,6 +2756,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220494</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113399397</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2886,6 +2986,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220619</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3001,6 +3106,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220964</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3116,6 +3226,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113221034</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3231,6 +3346,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113221041</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3354,6 +3474,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220681</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3477,6 +3602,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220716</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3607,8 +3737,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>